--- a/docs/quan-ly/Quan-ly-du-an.xlsx
+++ b/docs/quan-ly/Quan-ly-du-an.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thành viên" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$67,"Hoàn thành")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Hoàn thành")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$67,"Hoàn thành",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$69,"Hoàn thành",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -534,11 +534,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$67,"Đang làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Đang làm")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$67,"Đang làm",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$69,"Đang làm",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -549,11 +549,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$67,"Chưa làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Chưa làm")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$67,"Chưa làm",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$69,"Chưa làm",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -613,11 +613,11 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$67,"Sprint 1")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 1")</f>
         <v/>
       </c>
       <c r="C11" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$67,"Sprint 1",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 1",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -628,11 +628,11 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$67,"Sprint 1-2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 1-2")</f>
         <v/>
       </c>
       <c r="C12" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$67,"Sprint 1-2",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 1-2",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -643,11 +643,26 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$67,"Sprint 2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 2")</f>
         <v/>
       </c>
       <c r="C13" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$67,"Sprint 2",'Product backlog'!$F$2:$F$67)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 2",'Product backlog'!$F$2:$F$69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 3")</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 3",'Product backlog'!$F$2:$F$69)</f>
         <v/>
       </c>
     </row>
@@ -697,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1435,17 +1450,17 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Buổi 8</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>TC-10</t>
+          <t>TC-10, TC-33</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr"/>
@@ -1481,24 +1496,120 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Buổi 9</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>TC-42, TC-43</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>PB-17</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Kiểm thử</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Là đội phát triển, tôi muốn sửa các lỗi phát hiện khi kiểm thử để sản phẩm ổn định trước khi báo cáo</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>12 lỗi trong Bug log đã sửa, có test hồi quy; coverage gộp ≥ 80%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>TC-34..TC-40, TC-44, TC-45</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>PB-18</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Mục 7</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Là bệnh viện, tôi muốn phiên đăng nhập được thu hồi khi đổi mật khẩu/khóa và nhân viên tự đăng xuất khi bỏ máy</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Đổi mật khẩu/khóa/đổi vai trò thu hồi phiên; nhân viên không thao tác 30 phút tự đăng xuất</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>TC-38, TC-41</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J19"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Hoàn thành,Đang làm,Chưa làm"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cao,Trung bình,Thấp"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1633,49 +1744,49 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Kiểm thử</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Buổi 8</t>
+          <t>Buổi 8-9</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Kiểm thử đầy đủ, hiệu năng, sửa lỗi</t>
+          <t>Kiểm thử, sửa lỗi, thử tải, triển khai Docker, sao lưu</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>PB-15</t>
+          <t>PB-15..PB-18</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
+          <t>Hoàn thành (15/10/2026)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Triển khai</t>
+          <t>Báo cáo</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Buổi 9-10</t>
+          <t>Buổi 10</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Docker, báo cáo, tổng duyệt</t>
+          <t>Báo cáo, slide, tổng duyệt; thử push FCM thật</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>PB-16</t>
+          <t>PB-09 (phần còn lại)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1977,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2112,7 +2223,34 @@
           <t>37 unit + 48 e2e test pass; độ trễ cập nhật màn hình người nhà 113 ms</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>0372531</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 3: rà lỗi (12 lỗi đã sửa + 5 hạn chế, ghi Bug log), thử tải k6 100/500 người nhà, Docker + nginx + sao lưu, tự đăng xuất</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>53 unit + 56 e2e pass, coverage 94%; 500 người nhà: 0 lỗi, thông báo p95 1,04 s</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/quan-ly/Quan-ly-du-an.xlsx
+++ b/docs/quan-ly/Quan-ly-du-an.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thành viên" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Hoàn thành")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Hoàn thành")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$69,"Hoàn thành",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$71,"Hoàn thành",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -534,11 +534,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Đang làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Đang làm")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$69,"Đang làm",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$71,"Đang làm",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -549,11 +549,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$69,"Chưa làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Chưa làm")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$69,"Chưa làm",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$71,"Chưa làm",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -613,11 +613,11 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 1")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 1")</f>
         <v/>
       </c>
       <c r="C11" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 1",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 1",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -628,11 +628,11 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 1-2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 1-2")</f>
         <v/>
       </c>
       <c r="C12" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 1-2",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 1-2",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 2")</f>
         <v/>
       </c>
       <c r="C13" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 2",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 2",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -658,11 +658,26 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF('Product backlog'!$G$2:$G$69,"Sprint 3")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 3")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>SUMIF('Product backlog'!$G$2:$G$69,"Sprint 3",'Product backlog'!$F$2:$F$69)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 3",'Product backlog'!$F$2:$F$71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 4")</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 4",'Product backlog'!$F$2:$F$71)</f>
         <v/>
       </c>
     </row>
@@ -712,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1603,13 +1618,101 @@
       </c>
       <c r="J19" s="7" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>PB-19</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Buổi 9</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Là nhóm, tôi muốn có ảnh minh chứng cho từng test case để đưa vào báo cáo và chấm Rubric 3</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>20 kịch bản Playwright chạy lại được, ảnh đặt tên theo mã TC; ảnh kết quả Jest/k6/Docker dựng từ file kết quả thật</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>TC-01..TC-48</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>PB-20</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Buổi 9-10</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Là nhóm, tôi muốn có báo cáo 8 mục, slide và dữ liệu demo để bảo vệ đề tài</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Báo cáo Word có mục lục, hình, bảng; 14 slide có ghi chú; seed dữ liệu demo</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J21"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Hoàn thành,Đang làm,Chưa làm"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cao,Trung bình,Thấp"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1623,7 +1726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1771,25 +1874,52 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Buổi 9-10</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Minh chứng tự động, báo cáo 8 mục, slide, dữ liệu demo</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>PB-19, PB-20</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành (16/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
           <t>Báo cáo</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Buổi 10</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Báo cáo, slide, tổng duyệt; thử push FCM thật</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Buổi 10 + bảo vệ</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng duyệt, quay video dự phòng; thử push FCM thật nếu có Firebase</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>PB-09 (phần còn lại)</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -2088,7 +2218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2250,7 +2380,34 @@
           <t>53 unit + 56 e2e pass, coverage 94%; 500 người nhà: 0 lỗi, thông báo p95 1,04 s</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>1162c31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4: dữ liệu demo, 20 kịch bản Playwright + 36 ảnh minh chứng, sửa BUG-13..16, báo cáo Word 39 trang, 14 slide</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>47/48 test case đạt; 110 test Jest pass</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/quan-ly/Quan-ly-du-an.xlsx
+++ b/docs/quan-ly/Quan-ly-du-an.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thành viên" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product backlog'!$A$1:$J$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -519,11 +519,11 @@
         </is>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Hoàn thành")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$72,"Hoàn thành")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$71,"Hoàn thành",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$72,"Hoàn thành",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -534,11 +534,11 @@
         </is>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Đang làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$72,"Đang làm")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$71,"Đang làm",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$72,"Đang làm",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -549,11 +549,11 @@
         </is>
       </c>
       <c r="B6" s="3">
-        <f>COUNTIF('Product backlog'!$H$2:$H$71,"Chưa làm")</f>
+        <f>COUNTIF('Product backlog'!$H$2:$H$72,"Chưa làm")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>SUMIF('Product backlog'!$H$2:$H$71,"Chưa làm",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$H$2:$H$72,"Chưa làm",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -613,11 +613,11 @@
         </is>
       </c>
       <c r="B11" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 1")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$72,"Sprint 1")</f>
         <v/>
       </c>
       <c r="C11" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 1",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$72,"Sprint 1",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -628,11 +628,11 @@
         </is>
       </c>
       <c r="B12" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 1-2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$72,"Sprint 1-2")</f>
         <v/>
       </c>
       <c r="C12" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 1-2",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$72,"Sprint 1-2",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="B13" s="3">
-        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 2")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$72,"Sprint 2")</f>
         <v/>
       </c>
       <c r="C13" s="3">
-        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 2",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$72,"Sprint 2",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -658,11 +658,11 @@
         </is>
       </c>
       <c r="B14">
-        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 3")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$72,"Sprint 3")</f>
         <v/>
       </c>
       <c r="C14">
-        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 3",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$72,"Sprint 3",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -673,11 +673,11 @@
         </is>
       </c>
       <c r="B15">
-        <f>COUNTIF('Product backlog'!$G$2:$G$71,"Sprint 4")</f>
+        <f>COUNTIF('Product backlog'!$G$2:$G$72,"Sprint 4")</f>
         <v/>
       </c>
       <c r="C15">
-        <f>SUMIF('Product backlog'!$G$2:$G$71,"Sprint 4",'Product backlog'!$F$2:$F$71)</f>
+        <f>SUMIF('Product backlog'!$G$2:$G$72,"Sprint 4",'Product backlog'!$F$2:$F$72)</f>
         <v/>
       </c>
     </row>
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -807,12 +807,12 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Là người nhà, tôi muốn đăng ký/đăng nhập bằng SĐT hoặc email để dùng ứng dụng</t>
+          <t>Là nhân viên y tế/quản trị viên, tôi muốn đăng nhập bằng email và mật khẩu; người nhà thì không cần tài khoản</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Đăng ký, đăng nhập, đăng xuất, đổi mật khẩu; mật khẩu băm argon2</t>
+          <t>Chỉ nhân viên và quản trị đăng nhập; đổi mật khẩu thu hồi phiên cũ; seed sẵn 1 quản trị + 3 nhân viên; bỏ tự đăng ký</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>TC-11, TC-12, TC-13</t>
+          <t>TC-12, TC-13, TC-49, TC-50</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr"/>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Là nhân viên y tế, tôi muốn cấp mã/QR cho người nhà để họ tự theo dõi</t>
+          <t>Là nhân viên y tế, tôi muốn đăng ký số điện thoại và họ tên người nhà vào ca để họ tự theo dõi</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Mã ngẫu nhiên 8 ký tự, có hạn, dùng một lần, thu hồi được; QR chứa link</t>
+          <t>Đăng ký, xem danh sách, gỡ quyền người nhà của ca; không đăng ký cho ca đã kết thúc; SĐT nhân viên bị từ chối (thay cho mã/QR từ 17/10/2026)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>TC-04, TC-19</t>
+          <t>TC-11, TC-19, TC-36</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr"/>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Là người nhà, tôi muốn nhập mã hoặc quét QR để liên kết với bệnh nhân</t>
+          <t>Là người nhà, tôi muốn vào xem bằng SĐT, họ tên mình và họ tên bệnh nhân, không cần mật khẩu hay email</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Liên kết thành công; mã sai/hết hạn báo lỗi; sai 5 lần khóa 15 phút</t>
+          <t>Khớp với đăng ký của nhân viên thì vào xem; gõ không dấu vẫn được; sai 5 lần khóa 15 phút; phiên hết khi ca kết thúc</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>TC-03, TC-05, TC-22</t>
+          <t>TC-03, TC-04, TC-05, TC-22</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr"/>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Đang làm</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>TC-01, TC-09, TC-23..25, TC-31</t>
+          <t>TC-01, TC-09, TC-23..25, TC-31, TC-53, TC-54</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -1706,13 +1706,59 @@
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>PB-21</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>FR-01, FR-07</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Là bệnh viện, tôi muốn người nhà không phải tạo tài khoản: nhân viên đăng ký trước, người nhà nhập 3 thông tin để xem</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>API /auth/family-access và /surgeries/{id}/family-contacts; bỏ mã/QR và tự đăng ký; cập nhật web, test, tài liệu</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>TC-03..05, TC-11, TC-22, TC-39, TC-40, TC-49..51</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J21"/>
+  <autoFilter ref="A1:J22"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Hoàn thành,Đang làm,Chưa làm"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E2:E72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Cao,Trung bình,Thấp"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1803,7 +1849,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Luồng cốt lõi: xác thực, ca mổ, trạng thái, mã/QR, liên kết người nhà</t>
+          <t>Luồng cốt lõi: xác thực, ca mổ, trạng thái, liên kết người nhà (ban đầu bằng mã/QR)</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -1884,17 +1930,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Minh chứng tự động, báo cáo 8 mục, slide, dữ liệu demo</t>
+          <t>Minh chứng tự động, báo cáo 8 mục, slide, dữ liệu demo; đổi cách người nhà vào xem</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>PB-19, PB-20</t>
+          <t>PB-19..PB-21</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Hoàn thành (16/10/2026)</t>
+          <t>Hoàn thành (17/10/2026)</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2408,6 +2454,29 @@
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>ThienBao19</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Đổi cách người nhà vào xem: nhân viên đăng ký SĐT + họ tên người nhà, người nhà nhập SĐT + họ tên + tên bệnh nhân (không mật khẩu); bỏ mã/QR và tự đăng ký; seed 1 quản trị + 3 nhân viên; viết lại test, cập nhật tài liệu</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>54 unit + 56 e2e + 19 kịch bản Playwright đạt; 50/51 test case đạt</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
